--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run5/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run5/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8655,0.0230,0.0806,0.0513</t>
-  </si>
-  <si>
-    <t>0.0321,0.0188,0.0920,0.9381</t>
-  </si>
-  <si>
-    <t>0.7550,0.0223,0.0416,0.1963</t>
-  </si>
-  <si>
-    <t>0.3195,0.0167,0.0530,0.6833</t>
-  </si>
-  <si>
-    <t>0.9914,0.0044,0.0037,0.0012</t>
-  </si>
-  <si>
-    <t>0.9879,0.0083,0.0046,0.0017</t>
-  </si>
-  <si>
-    <t>0.9855,0.0090,0.0065,0.0018</t>
-  </si>
-  <si>
-    <t>0.9826,0.0094,0.0067,0.0027</t>
-  </si>
-  <si>
-    <t>0.9628,0.0344,0.0167,0.0033</t>
-  </si>
-  <si>
-    <t>0.9894,0.0076,0.0031,0.0015</t>
-  </si>
-  <si>
-    <t>0.9863,0.0098,0.0056,0.0016</t>
-  </si>
-  <si>
-    <t>0.9888,0.0051,0.0052,0.0020</t>
-  </si>
-  <si>
-    <t>0.5626,0.0342,0.5245,0.0111</t>
-  </si>
-  <si>
-    <t>0.2105,0.0609,0.7685,0.0089</t>
-  </si>
-  <si>
-    <t>0.4617,0.0186,0.7032,0.0034</t>
-  </si>
-  <si>
-    <t>0.0679,0.0202,0.9482,0.0034</t>
-  </si>
-  <si>
-    <t>0.3760,0.0333,0.7268,0.0129</t>
-  </si>
-  <si>
-    <t>0.0485,0.9420,0.0270,0.0023</t>
-  </si>
-  <si>
-    <t>0.0374,0.9445,0.0374,0.0024</t>
-  </si>
-  <si>
-    <t>0.2095,0.7979,0.0496,0.0084</t>
-  </si>
-  <si>
-    <t>0.0379,0.9446,0.0408,0.0026</t>
-  </si>
-  <si>
-    <t>0.0023,0.9939,0.0133,0.0003</t>
-  </si>
-  <si>
-    <t>0.3124,0.0190,0.7696,0.0177</t>
-  </si>
-  <si>
-    <t>0.1618,0.0265,0.8754,0.0083</t>
-  </si>
-  <si>
-    <t>0.1441,0.0195,0.9041,0.0080</t>
-  </si>
-  <si>
-    <t>0.1470,0.0157,0.8890,0.0072</t>
-  </si>
-  <si>
-    <t>0.0422,0.0080,0.9772,0.0013</t>
-  </si>
-  <si>
-    <t>0.1214,0.0087,0.9391,0.0066</t>
-  </si>
-  <si>
-    <t>0.0072,0.0041,0.9833,0.0139</t>
-  </si>
-  <si>
-    <t>0.4963,0.4991,0.0744,0.0062</t>
-  </si>
-  <si>
-    <t>0.4807,0.0670,0.5575,0.0118</t>
-  </si>
-  <si>
-    <t>0.0007,0.0044,0.9983,0.0005</t>
-  </si>
-  <si>
-    <t>0.0687,0.8406,0.1758,0.0122</t>
-  </si>
-  <si>
-    <t>0.6710,0.0790,0.2827,0.0315</t>
-  </si>
-  <si>
-    <t>0.2483,0.1746,0.6683,0.0183</t>
-  </si>
-  <si>
-    <t>0.4028,0.6854,0.0411,0.0105</t>
-  </si>
-  <si>
-    <t>0.0482,0.8653,0.2448,0.0087</t>
-  </si>
-  <si>
-    <t>0.0500,0.5584,0.6718,0.0413</t>
-  </si>
-  <si>
-    <t>0.0279,0.0133,0.9558,0.0266</t>
-  </si>
-  <si>
-    <t>0.0363,0.0974,0.9108,0.0249</t>
-  </si>
-  <si>
-    <t>0.0570,0.0138,0.9448,0.0178</t>
-  </si>
-  <si>
-    <t>0.0555,0.1057,0.9091,0.0099</t>
-  </si>
-  <si>
-    <t>0.0186,0.9365,0.1337,0.0095</t>
-  </si>
-  <si>
-    <t>0.0218,0.0510,0.9508,0.0116</t>
-  </si>
-  <si>
-    <t>0.3519,0.4386,0.2432,0.2143</t>
-  </si>
-  <si>
-    <t>0.0153,0.9619,0.0641,0.0086</t>
-  </si>
-  <si>
-    <t>0.0322,0.8969,0.2172,0.0124</t>
-  </si>
-  <si>
-    <t>0.0058,0.9691,0.1740,0.0065</t>
-  </si>
-  <si>
-    <t>0.0107,0.0240,0.9824,0.0028</t>
-  </si>
-  <si>
-    <t>0.0025,0.0437,0.9897,0.0020</t>
-  </si>
-  <si>
-    <t>0.0748,0.0081,0.9617,0.0039</t>
-  </si>
-  <si>
-    <t>0.0142,0.0044,0.9821,0.0095</t>
-  </si>
-  <si>
-    <t>0.0206,0.0574,0.9559,0.0096</t>
-  </si>
-  <si>
-    <t>0.0312,0.5004,0.8044,0.0155</t>
-  </si>
-  <si>
-    <t>0.9571,0.0272,0.0296,0.0035</t>
-  </si>
-  <si>
-    <t>0.9820,0.0081,0.0122,0.0029</t>
-  </si>
-  <si>
-    <t>0.9726,0.0281,0.0082,0.0036</t>
-  </si>
-  <si>
-    <t>0.0820,0.0446,0.9185,0.0105</t>
-  </si>
-  <si>
-    <t>0.9829,0.0076,0.0099,0.0028</t>
-  </si>
-  <si>
-    <t>0.9884,0.0063,0.0034,0.0019</t>
-  </si>
-  <si>
-    <t>0.9592,0.0416,0.0160,0.0050</t>
-  </si>
-  <si>
-    <t>0.0051,0.8077,0.8256,0.0035</t>
-  </si>
-  <si>
-    <t>0.0091,0.0383,0.9851,0.0017</t>
-  </si>
-  <si>
-    <t>0.0140,0.0745,0.9598,0.0138</t>
-  </si>
-  <si>
-    <t>0.0005,0.9792,0.6886,0.0004</t>
-  </si>
-  <si>
-    <t>0.0131,0.0085,0.9842,0.0036</t>
-  </si>
-  <si>
-    <t>0.0782,0.8600,0.1403,0.0088</t>
-  </si>
-  <si>
-    <t>0.0089,0.9880,0.0091,0.0010</t>
-  </si>
-  <si>
-    <t>0.5096,0.0230,0.6789,0.0085</t>
-  </si>
-  <si>
-    <t>0.4963,0.0846,0.5102,0.0122</t>
-  </si>
-  <si>
-    <t>0.0224,0.0182,0.9802,0.0016</t>
-  </si>
-  <si>
-    <t>0.0013,0.9247,0.8307,0.0008</t>
-  </si>
-  <si>
-    <t>0.0040,0.5485,0.9338,0.0024</t>
-  </si>
-  <si>
-    <t>0.0034,0.9443,0.5451,0.0028</t>
-  </si>
-  <si>
-    <t>0.0021,0.9118,0.7556,0.0013</t>
-  </si>
-  <si>
-    <t>0.0388,0.0074,0.0922,0.9203</t>
-  </si>
-  <si>
-    <t>0.0042,0.0121,0.0072,0.9954</t>
-  </si>
-  <si>
-    <t>0.0054,0.0063,0.0058,0.9951</t>
-  </si>
-  <si>
-    <t>0.0568,0.0210,0.0179,0.9563</t>
-  </si>
-  <si>
-    <t>0.0952,0.0086,0.0298,0.9191</t>
-  </si>
-  <si>
-    <t>0.0191,0.0170,0.0262,0.9791</t>
-  </si>
-  <si>
-    <t>0.0059,0.8493,0.7633,0.0033</t>
-  </si>
-  <si>
-    <t>0.0014,0.8721,0.9084,0.0008</t>
-  </si>
-  <si>
-    <t>0.0086,0.8648,0.6478,0.0059</t>
-  </si>
-  <si>
-    <t>0.0102,0.2248,0.9491,0.0077</t>
-  </si>
-  <si>
-    <t>0.0042,0.7799,0.8683,0.0023</t>
-  </si>
-  <si>
-    <t>0.0050,0.8166,0.8032,0.0029</t>
-  </si>
-  <si>
-    <t>0.9751,0.0143,0.0110,0.0035</t>
-  </si>
-  <si>
-    <t>0.9821,0.0122,0.0069,0.0024</t>
-  </si>
-  <si>
-    <t>0.9728,0.0198,0.0168,0.0021</t>
-  </si>
-  <si>
-    <t>0.9792,0.0170,0.0083,0.0026</t>
-  </si>
-  <si>
-    <t>0.9741,0.0242,0.0111,0.0023</t>
-  </si>
-  <si>
-    <t>0.9791,0.0161,0.0092,0.0028</t>
-  </si>
-  <si>
-    <t>0.9819,0.0092,0.0164,0.0025</t>
-  </si>
-  <si>
-    <t>0.9799,0.0194,0.0062,0.0020</t>
-  </si>
-  <si>
-    <t>0.9913,0.0043,0.0040,0.0013</t>
-  </si>
-  <si>
-    <t>0.9920,0.0042,0.0035,0.0011</t>
-  </si>
-  <si>
-    <t>0.9858,0.0073,0.0061,0.0025</t>
-  </si>
-  <si>
-    <t>0.9859,0.0060,0.0095,0.0021</t>
-  </si>
-  <si>
-    <t>0.9889,0.0069,0.0046,0.0016</t>
-  </si>
-  <si>
-    <t>0.9843,0.0115,0.0064,0.0021</t>
-  </si>
-  <si>
-    <t>0.9894,0.0053,0.0050,0.0018</t>
-  </si>
-  <si>
-    <t>0.9850,0.0114,0.0046,0.0022</t>
-  </si>
-  <si>
-    <t>0.0012,0.0013,0.9971,0.0023</t>
-  </si>
-  <si>
-    <t>0.0581,0.0145,0.9578,0.0046</t>
-  </si>
-  <si>
-    <t>0.5964,0.0635,0.4420,0.0265</t>
-  </si>
-  <si>
-    <t>0.2068,0.0114,0.8990,0.0026</t>
-  </si>
-  <si>
-    <t>0.0090,0.9843,0.0104,0.0012</t>
-  </si>
-  <si>
-    <t>0.0151,0.9785,0.0096,0.0021</t>
-  </si>
-  <si>
-    <t>0.1184,0.8834,0.0386,0.0056</t>
-  </si>
-  <si>
-    <t>0.1101,0.8754,0.0499,0.0072</t>
-  </si>
-  <si>
-    <t>0.0526,0.9366,0.0325,0.0035</t>
-  </si>
-  <si>
-    <t>0.0018,0.9959,0.0047,0.0006</t>
-  </si>
-  <si>
-    <t>0.1428,0.8601,0.0438,0.0081</t>
-  </si>
-  <si>
-    <t>0.5356,0.1090,0.4059,0.0280</t>
-  </si>
-  <si>
-    <t>0.2861,0.0351,0.7840,0.0096</t>
-  </si>
-  <si>
-    <t>0.5692,0.0512,0.4807,0.0126</t>
-  </si>
-  <si>
-    <t>0.4200,0.0233,0.7024,0.0070</t>
-  </si>
-  <si>
-    <t>0.3530,0.0783,0.5434,0.1553</t>
-  </si>
-  <si>
-    <t>0.0081,0.9737,0.0760,0.0020</t>
-  </si>
-  <si>
-    <t>0.0044,0.9815,0.0470,0.0051</t>
-  </si>
-  <si>
-    <t>0.0337,0.9308,0.0579,0.0170</t>
-  </si>
-  <si>
-    <t>0.0016,0.9799,0.3869,0.0013</t>
-  </si>
-  <si>
-    <t>0.1451,0.8097,0.1079,0.0085</t>
-  </si>
-  <si>
-    <t>0.4270,0.5431,0.1021,0.0096</t>
-  </si>
-  <si>
-    <t>0.3967,0.6723,0.0381,0.0067</t>
-  </si>
-  <si>
-    <t>0.9379,0.0633,0.0261,0.0079</t>
-  </si>
-  <si>
-    <t>0.9862,0.0044,0.0076,0.0035</t>
-  </si>
-  <si>
-    <t>0.9859,0.0056,0.0108,0.0021</t>
-  </si>
-  <si>
-    <t>0.9589,0.0141,0.0368,0.0061</t>
-  </si>
-  <si>
-    <t>0.9870,0.0042,0.0095,0.0018</t>
-  </si>
-  <si>
-    <t>0.9468,0.0174,0.0402,0.0120</t>
-  </si>
-  <si>
-    <t>0.9739,0.0099,0.0168,0.0046</t>
-  </si>
-  <si>
-    <t>0.9885,0.0043,0.0067,0.0026</t>
-  </si>
-  <si>
-    <t>0.0237,0.6096,0.7776,0.0150</t>
-  </si>
-  <si>
-    <t>0.0113,0.6282,0.8532,0.0058</t>
-  </si>
-  <si>
-    <t>0.0180,0.0479,0.9692,0.0033</t>
-  </si>
-  <si>
-    <t>0.0295,0.1815,0.9109,0.0065</t>
-  </si>
-  <si>
-    <t>0.7495,0.0332,0.2881,0.0232</t>
-  </si>
-  <si>
-    <t>0.7955,0.0352,0.2311,0.0182</t>
-  </si>
-  <si>
-    <t>0.3015,0.0121,0.7836,0.0253</t>
-  </si>
-  <si>
-    <t>0.4735,0.0729,0.5386,0.0130</t>
-  </si>
-  <si>
-    <t>0.2890,0.0088,0.0519,0.6557</t>
-  </si>
-  <si>
-    <t>0.0004,0.0053,0.0114,0.9984</t>
-  </si>
-  <si>
-    <t>0.0028,0.0083,0.0126,0.9952</t>
-  </si>
-  <si>
-    <t>0.0258,0.0035,0.0410,0.9558</t>
-  </si>
-  <si>
-    <t>0.0045,0.8354,0.7965,0.0033</t>
-  </si>
-  <si>
-    <t>0.9827,0.0052,0.0165,0.0018</t>
-  </si>
-  <si>
-    <t>0.6382,0.2965,0.1309,0.0174</t>
-  </si>
-  <si>
-    <t>0.9805,0.0075,0.0163,0.0020</t>
-  </si>
-  <si>
-    <t>0.6434,0.4076,0.0545,0.0119</t>
-  </si>
-  <si>
-    <t>0.9548,0.0123,0.0211,0.0139</t>
-  </si>
-  <si>
-    <t>0.5272,0.0250,0.2427,0.2090</t>
-  </si>
-  <si>
-    <t>0.9702,0.0088,0.0224,0.0058</t>
-  </si>
-  <si>
-    <t>0.0280,0.0597,0.9352,0.0171</t>
-  </si>
-  <si>
-    <t>0.8230,0.0099,0.0816,0.0744</t>
-  </si>
-  <si>
-    <t>0.8577,0.0123,0.1737,0.0146</t>
-  </si>
-  <si>
-    <t>0.2880,0.7161,0.0697,0.0273</t>
-  </si>
-  <si>
-    <t>0.8927,0.0418,0.0827,0.0186</t>
-  </si>
-  <si>
-    <t>0.7650,0.0163,0.3861,0.0065</t>
-  </si>
-  <si>
-    <t>0.1644,0.7834,0.1063,0.0221</t>
-  </si>
-  <si>
-    <t>0.7166,0.1040,0.2170,0.0089</t>
-  </si>
-  <si>
-    <t>0.8448,0.0331,0.1755,0.0099</t>
-  </si>
-  <si>
-    <t>0.9865,0.0052,0.0080,0.0023</t>
-  </si>
-  <si>
-    <t>0.9712,0.0145,0.0151,0.0061</t>
-  </si>
-  <si>
-    <t>0.9903,0.0037,0.0046,0.0019</t>
-  </si>
-  <si>
-    <t>0.9846,0.0047,0.0069,0.0047</t>
-  </si>
-  <si>
-    <t>0.9762,0.0111,0.0105,0.0039</t>
-  </si>
-  <si>
-    <t>0.9758,0.0112,0.0183,0.0026</t>
-  </si>
-  <si>
-    <t>0.9864,0.0054,0.0059,0.0027</t>
-  </si>
-  <si>
-    <t>0.9893,0.0045,0.0047,0.0023</t>
-  </si>
-  <si>
-    <t>0.2128,0.7846,0.0487,0.0106</t>
-  </si>
-  <si>
-    <t>0.6528,0.3484,0.0658,0.0093</t>
-  </si>
-  <si>
-    <t>0.5578,0.4947,0.0496,0.0074</t>
-  </si>
-  <si>
-    <t>0.0867,0.0528,0.9157,0.0045</t>
-  </si>
-  <si>
-    <t>0.9290,0.0865,0.0143,0.0048</t>
-  </si>
-  <si>
-    <t>0.9452,0.0474,0.0185,0.0046</t>
-  </si>
-  <si>
-    <t>0.9768,0.0148,0.0094,0.0028</t>
-  </si>
-  <si>
-    <t>0.9050,0.0663,0.0494,0.0072</t>
-  </si>
-  <si>
-    <t>0.0122,0.0156,0.9883,0.0015</t>
-  </si>
-  <si>
-    <t>0.8584,0.0956,0.0670,0.0132</t>
-  </si>
-  <si>
-    <t>0.0103,0.0101,0.9897,0.0013</t>
-  </si>
-  <si>
-    <t>0.0084,0.1434,0.9679,0.0036</t>
-  </si>
-  <si>
-    <t>0.0815,0.0103,0.9451,0.0063</t>
-  </si>
-  <si>
-    <t>0.0131,0.0971,0.9706,0.0020</t>
-  </si>
-  <si>
-    <t>0.0861,0.0171,0.9422,0.0038</t>
-  </si>
-  <si>
-    <t>0.0214,0.0058,0.9811,0.0033</t>
-  </si>
-  <si>
-    <t>0.0076,0.0076,0.9880,0.0026</t>
-  </si>
-  <si>
-    <t>0.3956,0.0491,0.6428,0.0120</t>
-  </si>
-  <si>
-    <t>0.2866,0.0113,0.8600,0.0022</t>
-  </si>
-  <si>
-    <t>0.4274,0.1197,0.4719,0.0157</t>
-  </si>
-  <si>
-    <t>0.3636,0.1097,0.5706,0.0101</t>
-  </si>
-  <si>
-    <t>0.1339,0.3085,0.6321,0.0153</t>
-  </si>
-  <si>
-    <t>0.4575,0.0132,0.7189,0.0055</t>
-  </si>
-  <si>
-    <t>0.6595,0.0130,0.5133,0.0064</t>
-  </si>
-  <si>
-    <t>0.4870,0.0265,0.6405,0.0062</t>
-  </si>
-  <si>
-    <t>0.7389,0.2825,0.0555,0.0046</t>
-  </si>
-  <si>
-    <t>0.7901,0.2109,0.0552,0.0059</t>
-  </si>
-  <si>
-    <t>0.8345,0.1512,0.0577,0.0052</t>
-  </si>
-  <si>
-    <t>0.9389,0.0509,0.0341,0.0041</t>
-  </si>
-  <si>
-    <t>0.7574,0.2851,0.0534,0.0071</t>
-  </si>
-  <si>
-    <t>0.3288,0.3466,0.3103,0.0202</t>
-  </si>
-  <si>
-    <t>0.5766,0.0261,0.5346,0.0179</t>
-  </si>
-  <si>
-    <t>0.6755,0.0112,0.4836,0.0063</t>
-  </si>
-  <si>
-    <t>0.4986,0.0252,0.6321,0.0110</t>
-  </si>
-  <si>
-    <t>0.3305,0.0186,0.7542,0.0152</t>
-  </si>
-  <si>
-    <t>0.0188,0.0182,0.9723,0.0076</t>
-  </si>
-  <si>
-    <t>0.0293,0.1318,0.9015,0.0266</t>
-  </si>
-  <si>
-    <t>0.0268,0.1691,0.9122,0.0135</t>
-  </si>
-  <si>
-    <t>0.0739,0.2135,0.8073,0.0361</t>
-  </si>
-  <si>
-    <t>0.0122,0.5328,0.8839,0.0070</t>
-  </si>
-  <si>
-    <t>0.9804,0.0158,0.0082,0.0025</t>
-  </si>
-  <si>
-    <t>0.9790,0.0122,0.0137,0.0023</t>
-  </si>
-  <si>
-    <t>0.9771,0.0180,0.0063,0.0036</t>
-  </si>
-  <si>
-    <t>0.9805,0.0156,0.0057,0.0028</t>
-  </si>
-  <si>
-    <t>0.9721,0.0217,0.0100,0.0040</t>
-  </si>
-  <si>
-    <t>0.9639,0.0278,0.0160,0.0049</t>
-  </si>
-  <si>
-    <t>0.9740,0.0210,0.0097,0.0050</t>
-  </si>
-  <si>
-    <t>0.9667,0.0145,0.0168,0.0078</t>
-  </si>
-  <si>
-    <t>0.0917,0.0072,0.9522,0.0045</t>
-  </si>
-  <si>
-    <t>0.3303,0.0431,0.7337,0.0106</t>
-  </si>
-  <si>
-    <t>0.9055,0.0104,0.1149,0.0123</t>
-  </si>
-  <si>
-    <t>0.0083,0.0025,0.9933,0.0015</t>
-  </si>
-  <si>
-    <t>0.0014,0.0060,0.9942,0.0043</t>
-  </si>
-  <si>
-    <t>0.0107,0.0492,0.9724,0.0022</t>
-  </si>
-  <si>
-    <t>0.0016,0.0059,0.9956,0.0023</t>
-  </si>
-  <si>
-    <t>0.0544,0.0099,0.9695,0.0024</t>
-  </si>
-  <si>
-    <t>0.0020,0.0914,0.9909,0.0016</t>
-  </si>
-  <si>
-    <t>0.0149,0.0759,0.9541,0.0114</t>
-  </si>
-  <si>
-    <t>0.1970,0.0480,0.8223,0.0122</t>
-  </si>
-  <si>
-    <t>0.4954,0.0199,0.6408,0.0104</t>
-  </si>
-  <si>
-    <t>0.6496,0.0121,0.3808,0.0295</t>
-  </si>
-  <si>
-    <t>0.8373,0.0498,0.1196,0.0198</t>
-  </si>
-  <si>
-    <t>0.9576,0.0507,0.0100,0.0055</t>
-  </si>
-  <si>
-    <t>0.9847,0.0084,0.0091,0.0021</t>
-  </si>
-  <si>
-    <t>0.9868,0.0092,0.0048,0.0016</t>
-  </si>
-  <si>
-    <t>0.9720,0.0227,0.0156,0.0021</t>
-  </si>
-  <si>
-    <t>0.9838,0.0137,0.0051,0.0025</t>
-  </si>
-  <si>
-    <t>0.9536,0.0509,0.0143,0.0032</t>
-  </si>
-  <si>
-    <t>0.9796,0.0208,0.0059,0.0018</t>
-  </si>
-  <si>
-    <t>0.9780,0.0183,0.0041,0.0043</t>
-  </si>
-  <si>
-    <t>0.1129,0.0285,0.9051,0.0058</t>
-  </si>
-  <si>
-    <t>0.0082,0.0408,0.9821,0.0023</t>
-  </si>
-  <si>
-    <t>0.0065,0.1561,0.9720,0.0042</t>
-  </si>
-  <si>
-    <t>0.0685,0.0388,0.9252,0.0040</t>
-  </si>
-  <si>
-    <t>0.0097,0.0049,0.9855,0.0050</t>
-  </si>
-  <si>
-    <t>0.0981,0.0206,0.8880,0.0437</t>
-  </si>
-  <si>
-    <t>0.0433,0.0098,0.9197,0.0594</t>
-  </si>
-  <si>
-    <t>0.0158,0.0116,0.9037,0.1409</t>
-  </si>
-  <si>
-    <t>0.9272,0.0056,0.0429,0.0237</t>
-  </si>
-  <si>
-    <t>0.0795,0.0434,0.0528,0.9243</t>
-  </si>
-  <si>
-    <t>0.1137,0.0052,0.0348,0.8772</t>
-  </si>
-  <si>
-    <t>0.0140,0.0021,0.0136,0.9861</t>
-  </si>
-  <si>
-    <t>0.0088,0.0065,0.0058,0.9934</t>
-  </si>
-  <si>
-    <t>0.5339,0.0295,0.0999,0.3564</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.7620,0.0249,0.3489,0.0143</t>
+  </si>
+  <si>
+    <t>0.0194,0.0111,0.0249,0.9785</t>
+  </si>
+  <si>
+    <t>0.3473,0.0244,0.0195,0.6742</t>
+  </si>
+  <si>
+    <t>0.3369,0.0174,0.0360,0.7023</t>
+  </si>
+  <si>
+    <t>0.9904,0.0041,0.0055,0.0019</t>
+  </si>
+  <si>
+    <t>0.9807,0.0167,0.0053,0.0029</t>
+  </si>
+  <si>
+    <t>0.9802,0.0124,0.0110,0.0023</t>
+  </si>
+  <si>
+    <t>0.9858,0.0064,0.0051,0.0035</t>
+  </si>
+  <si>
+    <t>0.9763,0.0212,0.0075,0.0028</t>
+  </si>
+  <si>
+    <t>0.9738,0.0264,0.0072,0.0025</t>
+  </si>
+  <si>
+    <t>0.9888,0.0060,0.0058,0.0015</t>
+  </si>
+  <si>
+    <t>0.9876,0.0061,0.0041,0.0025</t>
+  </si>
+  <si>
+    <t>0.6302,0.0189,0.5070,0.0081</t>
+  </si>
+  <si>
+    <t>0.1755,0.0711,0.7770,0.0117</t>
+  </si>
+  <si>
+    <t>0.3691,0.0508,0.6886,0.0072</t>
+  </si>
+  <si>
+    <t>0.1236,0.0217,0.9201,0.0047</t>
+  </si>
+  <si>
+    <t>0.4489,0.0152,0.7454,0.0047</t>
+  </si>
+  <si>
+    <t>0.0651,0.9215,0.0409,0.0035</t>
+  </si>
+  <si>
+    <t>0.0161,0.9730,0.0207,0.0010</t>
+  </si>
+  <si>
+    <t>0.2979,0.7671,0.0321,0.0101</t>
+  </si>
+  <si>
+    <t>0.0884,0.9105,0.0301,0.0034</t>
+  </si>
+  <si>
+    <t>0.0020,0.9944,0.0115,0.0003</t>
+  </si>
+  <si>
+    <t>0.4707,0.0133,0.6742,0.0154</t>
+  </si>
+  <si>
+    <t>0.3183,0.0363,0.7446,0.0128</t>
+  </si>
+  <si>
+    <t>0.0531,0.0080,0.9612,0.0067</t>
+  </si>
+  <si>
+    <t>0.1817,0.0157,0.8903,0.0047</t>
+  </si>
+  <si>
+    <t>0.0654,0.0043,0.9748,0.0014</t>
+  </si>
+  <si>
+    <t>0.1176,0.0114,0.9230,0.0091</t>
+  </si>
+  <si>
+    <t>0.0083,0.0022,0.9882,0.0076</t>
+  </si>
+  <si>
+    <t>0.2466,0.6458,0.1547,0.0085</t>
+  </si>
+  <si>
+    <t>0.2941,0.0326,0.7801,0.0164</t>
+  </si>
+  <si>
+    <t>0.0035,0.0192,0.9926,0.0013</t>
+  </si>
+  <si>
+    <t>0.0577,0.7969,0.2945,0.0084</t>
+  </si>
+  <si>
+    <t>0.7498,0.1262,0.1315,0.0530</t>
+  </si>
+  <si>
+    <t>0.5962,0.0947,0.3861,0.0291</t>
+  </si>
+  <si>
+    <t>0.6379,0.4556,0.0262,0.0077</t>
+  </si>
+  <si>
+    <t>0.1000,0.8299,0.1709,0.0133</t>
+  </si>
+  <si>
+    <t>0.0118,0.8880,0.4136,0.0143</t>
+  </si>
+  <si>
+    <t>0.0132,0.0298,0.9566,0.0386</t>
+  </si>
+  <si>
+    <t>0.0318,0.0848,0.9335,0.0190</t>
+  </si>
+  <si>
+    <t>0.0546,0.0193,0.9316,0.0273</t>
+  </si>
+  <si>
+    <t>0.0472,0.0722,0.9266,0.0065</t>
+  </si>
+  <si>
+    <t>0.0081,0.9589,0.1623,0.0036</t>
+  </si>
+  <si>
+    <t>0.0356,0.1311,0.9075,0.0102</t>
+  </si>
+  <si>
+    <t>0.2949,0.4149,0.1317,0.4016</t>
+  </si>
+  <si>
+    <t>0.0270,0.9346,0.0571,0.0337</t>
+  </si>
+  <si>
+    <t>0.0234,0.9321,0.1301,0.0085</t>
+  </si>
+  <si>
+    <t>0.0141,0.9602,0.0934,0.0076</t>
+  </si>
+  <si>
+    <t>0.0111,0.0289,0.9816,0.0019</t>
+  </si>
+  <si>
+    <t>0.0027,0.0457,0.9899,0.0016</t>
+  </si>
+  <si>
+    <t>0.0433,0.0093,0.9698,0.0035</t>
+  </si>
+  <si>
+    <t>0.0137,0.0056,0.9828,0.0068</t>
+  </si>
+  <si>
+    <t>0.0059,0.0146,0.9894,0.0029</t>
+  </si>
+  <si>
+    <t>0.0069,0.7128,0.8536,0.0037</t>
+  </si>
+  <si>
+    <t>0.9554,0.0298,0.0282,0.0037</t>
+  </si>
+  <si>
+    <t>0.9813,0.0082,0.0117,0.0031</t>
+  </si>
+  <si>
+    <t>0.9738,0.0169,0.0136,0.0031</t>
+  </si>
+  <si>
+    <t>0.0366,0.0349,0.9589,0.0033</t>
+  </si>
+  <si>
+    <t>0.9732,0.0119,0.0251,0.0031</t>
+  </si>
+  <si>
+    <t>0.9888,0.0055,0.0065,0.0018</t>
+  </si>
+  <si>
+    <t>0.9288,0.0603,0.0367,0.0055</t>
+  </si>
+  <si>
+    <t>0.0017,0.9110,0.8719,0.0012</t>
+  </si>
+  <si>
+    <t>0.0060,0.0362,0.9861,0.0027</t>
+  </si>
+  <si>
+    <t>0.0193,0.0232,0.9699,0.0091</t>
+  </si>
+  <si>
+    <t>0.0012,0.9185,0.8577,0.0014</t>
+  </si>
+  <si>
+    <t>0.0022,0.0029,0.9946,0.0043</t>
+  </si>
+  <si>
+    <t>0.0235,0.9577,0.0435,0.0026</t>
+  </si>
+  <si>
+    <t>0.0021,0.9964,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.8374,0.0117,0.2872,0.0040</t>
+  </si>
+  <si>
+    <t>0.5269,0.0819,0.4903,0.0143</t>
+  </si>
+  <si>
+    <t>0.0570,0.0417,0.9399,0.0023</t>
+  </si>
+  <si>
+    <t>0.0073,0.8475,0.7410,0.0042</t>
+  </si>
+  <si>
+    <t>0.0059,0.6070,0.9090,0.0024</t>
+  </si>
+  <si>
+    <t>0.0014,0.9835,0.2285,0.0015</t>
+  </si>
+  <si>
+    <t>0.0018,0.9333,0.7785,0.0014</t>
+  </si>
+  <si>
+    <t>0.0141,0.0201,0.0353,0.9792</t>
+  </si>
+  <si>
+    <t>0.0125,0.0088,0.0096,0.9895</t>
+  </si>
+  <si>
+    <t>0.0073,0.0079,0.0095,0.9925</t>
+  </si>
+  <si>
+    <t>0.0684,0.0082,0.0175,0.9533</t>
+  </si>
+  <si>
+    <t>0.0859,0.0052,0.0154,0.9385</t>
+  </si>
+  <si>
+    <t>0.0141,0.0122,0.0223,0.9840</t>
+  </si>
+  <si>
+    <t>0.0020,0.9488,0.6479,0.0013</t>
+  </si>
+  <si>
+    <t>0.0044,0.5552,0.9365,0.0030</t>
+  </si>
+  <si>
+    <t>0.0063,0.7298,0.8558,0.0032</t>
+  </si>
+  <si>
+    <t>0.0053,0.6411,0.9175,0.0032</t>
+  </si>
+  <si>
+    <t>0.0029,0.8171,0.8724,0.0017</t>
+  </si>
+  <si>
+    <t>0.0054,0.8819,0.6949,0.0032</t>
+  </si>
+  <si>
+    <t>0.9876,0.0065,0.0055,0.0017</t>
+  </si>
+  <si>
+    <t>0.9740,0.0232,0.0105,0.0029</t>
+  </si>
+  <si>
+    <t>0.9449,0.0639,0.0152,0.0037</t>
+  </si>
+  <si>
+    <t>0.9825,0.0133,0.0068,0.0025</t>
+  </si>
+  <si>
+    <t>0.9748,0.0234,0.0068,0.0030</t>
+  </si>
+  <si>
+    <t>0.9842,0.0118,0.0077,0.0016</t>
+  </si>
+  <si>
+    <t>0.9830,0.0123,0.0085,0.0026</t>
+  </si>
+  <si>
+    <t>0.9817,0.0136,0.0084,0.0020</t>
+  </si>
+  <si>
+    <t>0.9919,0.0034,0.0025,0.0022</t>
+  </si>
+  <si>
+    <t>0.9823,0.0105,0.0090,0.0023</t>
+  </si>
+  <si>
+    <t>0.9886,0.0076,0.0034,0.0016</t>
+  </si>
+  <si>
+    <t>0.9879,0.0066,0.0061,0.0014</t>
+  </si>
+  <si>
+    <t>0.9914,0.0047,0.0030,0.0016</t>
+  </si>
+  <si>
+    <t>0.9725,0.0257,0.0068,0.0034</t>
+  </si>
+  <si>
+    <t>0.9807,0.0113,0.0080,0.0029</t>
+  </si>
+  <si>
+    <t>0.9889,0.0050,0.0063,0.0019</t>
+  </si>
+  <si>
+    <t>0.0055,0.0029,0.9957,0.0007</t>
+  </si>
+  <si>
+    <t>0.0551,0.0140,0.9561,0.0072</t>
+  </si>
+  <si>
+    <t>0.6496,0.0338,0.4153,0.0195</t>
+  </si>
+  <si>
+    <t>0.0546,0.0047,0.9726,0.0031</t>
+  </si>
+  <si>
+    <t>0.0167,0.9757,0.0148,0.0014</t>
+  </si>
+  <si>
+    <t>0.0177,0.9723,0.0189,0.0014</t>
+  </si>
+  <si>
+    <t>0.1012,0.8791,0.0652,0.0089</t>
+  </si>
+  <si>
+    <t>0.1651,0.8325,0.0533,0.0092</t>
+  </si>
+  <si>
+    <t>0.0132,0.9787,0.0178,0.0011</t>
+  </si>
+  <si>
+    <t>0.0024,0.9938,0.0127,0.0004</t>
+  </si>
+  <si>
+    <t>0.3890,0.5415,0.1038,0.0079</t>
+  </si>
+  <si>
+    <t>0.4192,0.1681,0.4319,0.0253</t>
+  </si>
+  <si>
+    <t>0.2562,0.0215,0.8460,0.0065</t>
+  </si>
+  <si>
+    <t>0.7341,0.0386,0.2761,0.0158</t>
+  </si>
+  <si>
+    <t>0.5517,0.0243,0.5921,0.0084</t>
+  </si>
+  <si>
+    <t>0.3361,0.1083,0.4480,0.2640</t>
+  </si>
+  <si>
+    <t>0.0108,0.9632,0.1044,0.0051</t>
+  </si>
+  <si>
+    <t>0.0124,0.9691,0.0517,0.0037</t>
+  </si>
+  <si>
+    <t>0.0914,0.8488,0.1065,0.0272</t>
+  </si>
+  <si>
+    <t>0.0009,0.9888,0.1932,0.0017</t>
+  </si>
+  <si>
+    <t>0.0637,0.8991,0.0849,0.0052</t>
+  </si>
+  <si>
+    <t>0.4208,0.5722,0.0821,0.0126</t>
+  </si>
+  <si>
+    <t>0.5888,0.4731,0.0535,0.0080</t>
+  </si>
+  <si>
+    <t>0.8532,0.1274,0.0631,0.0080</t>
+  </si>
+  <si>
+    <t>0.9789,0.0077,0.0142,0.0037</t>
+  </si>
+  <si>
+    <t>0.9794,0.0076,0.0108,0.0042</t>
+  </si>
+  <si>
+    <t>0.9803,0.0061,0.0173,0.0026</t>
+  </si>
+  <si>
+    <t>0.9884,0.0047,0.0048,0.0019</t>
+  </si>
+  <si>
+    <t>0.9543,0.0092,0.0569,0.0056</t>
+  </si>
+  <si>
+    <t>0.9780,0.0076,0.0143,0.0048</t>
+  </si>
+  <si>
+    <t>0.9642,0.0176,0.0141,0.0069</t>
+  </si>
+  <si>
+    <t>0.0116,0.7934,0.7279,0.0064</t>
+  </si>
+  <si>
+    <t>0.0078,0.6582,0.8768,0.0036</t>
+  </si>
+  <si>
+    <t>0.0475,0.0253,0.9541,0.0046</t>
+  </si>
+  <si>
+    <t>0.0334,0.1315,0.9132,0.0103</t>
+  </si>
+  <si>
+    <t>0.9023,0.0131,0.1164,0.0082</t>
+  </si>
+  <si>
+    <t>0.7213,0.0459,0.3133,0.0078</t>
+  </si>
+  <si>
+    <t>0.1257,0.0060,0.9471,0.0036</t>
+  </si>
+  <si>
+    <t>0.4743,0.0196,0.6657,0.0075</t>
+  </si>
+  <si>
+    <t>0.0381,0.0050,0.0044,0.9799</t>
+  </si>
+  <si>
+    <t>0.0018,0.0048,0.0680,0.9885</t>
+  </si>
+  <si>
+    <t>0.0031,0.0135,0.0196,0.9936</t>
+  </si>
+  <si>
+    <t>0.0671,0.0042,0.0103,0.9550</t>
+  </si>
+  <si>
+    <t>0.0016,0.9292,0.8036,0.0014</t>
+  </si>
+  <si>
+    <t>0.9857,0.0064,0.0065,0.0023</t>
+  </si>
+  <si>
+    <t>0.2172,0.8072,0.0420,0.0166</t>
+  </si>
+  <si>
+    <t>0.9768,0.0081,0.0161,0.0031</t>
+  </si>
+  <si>
+    <t>0.4337,0.6009,0.0608,0.0108</t>
+  </si>
+  <si>
+    <t>0.9673,0.0057,0.0128,0.0130</t>
+  </si>
+  <si>
+    <t>0.3515,0.0139,0.2988,0.2792</t>
+  </si>
+  <si>
+    <t>0.9561,0.0144,0.0323,0.0085</t>
+  </si>
+  <si>
+    <t>0.0200,0.0657,0.9521,0.0098</t>
+  </si>
+  <si>
+    <t>0.6673,0.0072,0.1122,0.1678</t>
+  </si>
+  <si>
+    <t>0.8684,0.0188,0.0881,0.0350</t>
+  </si>
+  <si>
+    <t>0.1999,0.7453,0.1054,0.0197</t>
+  </si>
+  <si>
+    <t>0.7908,0.0878,0.1489,0.0216</t>
+  </si>
+  <si>
+    <t>0.8651,0.0234,0.1908,0.0058</t>
+  </si>
+  <si>
+    <t>0.3271,0.5967,0.1198,0.0326</t>
+  </si>
+  <si>
+    <t>0.6736,0.0433,0.4304,0.0050</t>
+  </si>
+  <si>
+    <t>0.4376,0.4714,0.1486,0.0224</t>
+  </si>
+  <si>
+    <t>0.9848,0.0066,0.0083,0.0029</t>
+  </si>
+  <si>
+    <t>0.9839,0.0070,0.0075,0.0037</t>
+  </si>
+  <si>
+    <t>0.9896,0.0058,0.0032,0.0018</t>
+  </si>
+  <si>
+    <t>0.9856,0.0048,0.0104,0.0028</t>
+  </si>
+  <si>
+    <t>0.9841,0.0062,0.0064,0.0032</t>
+  </si>
+  <si>
+    <t>0.9648,0.0172,0.0284,0.0043</t>
+  </si>
+  <si>
+    <t>0.9756,0.0097,0.0161,0.0047</t>
+  </si>
+  <si>
+    <t>0.9871,0.0052,0.0065,0.0028</t>
+  </si>
+  <si>
+    <t>0.5555,0.4979,0.0407,0.0093</t>
+  </si>
+  <si>
+    <t>0.8912,0.1062,0.0380,0.0070</t>
+  </si>
+  <si>
+    <t>0.2515,0.7848,0.0335,0.0086</t>
+  </si>
+  <si>
+    <t>0.4706,0.1326,0.4335,0.0127</t>
+  </si>
+  <si>
+    <t>0.9631,0.0177,0.0318,0.0024</t>
+  </si>
+  <si>
+    <t>0.8637,0.0946,0.0631,0.0167</t>
+  </si>
+  <si>
+    <t>0.9420,0.0512,0.0208,0.0067</t>
+  </si>
+  <si>
+    <t>0.7967,0.2082,0.0434,0.0131</t>
+  </si>
+  <si>
+    <t>0.0035,0.0281,0.9929,0.0006</t>
+  </si>
+  <si>
+    <t>0.9537,0.0252,0.0310,0.0057</t>
+  </si>
+  <si>
+    <t>0.0074,0.0148,0.9867,0.0036</t>
+  </si>
+  <si>
+    <t>0.0095,0.3178,0.9453,0.0046</t>
+  </si>
+  <si>
+    <t>0.0150,0.0081,0.9815,0.0051</t>
+  </si>
+  <si>
+    <t>0.0045,0.0532,0.9920,0.0003</t>
+  </si>
+  <si>
+    <t>0.1504,0.0101,0.9249,0.0026</t>
+  </si>
+  <si>
+    <t>0.0076,0.0070,0.9894,0.0033</t>
+  </si>
+  <si>
+    <t>0.0070,0.0123,0.9881,0.0021</t>
+  </si>
+  <si>
+    <t>0.3903,0.0499,0.6527,0.0144</t>
+  </si>
+  <si>
+    <t>0.3271,0.0133,0.8237,0.0042</t>
+  </si>
+  <si>
+    <t>0.7264,0.0269,0.3365,0.0150</t>
+  </si>
+  <si>
+    <t>0.2641,0.2063,0.5290,0.0109</t>
+  </si>
+  <si>
+    <t>0.3430,0.0606,0.6785,0.0110</t>
+  </si>
+  <si>
+    <t>0.5801,0.0847,0.4190,0.0174</t>
+  </si>
+  <si>
+    <t>0.5013,0.0112,0.6440,0.0110</t>
+  </si>
+  <si>
+    <t>0.4406,0.0291,0.6583,0.0102</t>
+  </si>
+  <si>
+    <t>0.5751,0.4247,0.0750,0.0053</t>
+  </si>
+  <si>
+    <t>0.1849,0.8423,0.0401,0.0045</t>
+  </si>
+  <si>
+    <t>0.7081,0.3293,0.0504,0.0074</t>
+  </si>
+  <si>
+    <t>0.9740,0.0261,0.0091,0.0031</t>
+  </si>
+  <si>
+    <t>0.9452,0.0783,0.0115,0.0029</t>
+  </si>
+  <si>
+    <t>0.5520,0.0587,0.4579,0.0366</t>
+  </si>
+  <si>
+    <t>0.6536,0.0123,0.5213,0.0100</t>
+  </si>
+  <si>
+    <t>0.7225,0.0378,0.2775,0.0373</t>
+  </si>
+  <si>
+    <t>0.3793,0.1238,0.5580,0.0224</t>
+  </si>
+  <si>
+    <t>0.7464,0.0291,0.2627,0.0280</t>
+  </si>
+  <si>
+    <t>0.0248,0.0091,0.9722,0.0093</t>
+  </si>
+  <si>
+    <t>0.0106,0.1317,0.9463,0.0137</t>
+  </si>
+  <si>
+    <t>0.0204,0.0946,0.9490,0.0125</t>
+  </si>
+  <si>
+    <t>0.0390,0.2867,0.8507,0.0198</t>
+  </si>
+  <si>
+    <t>0.0342,0.1036,0.9265,0.0101</t>
+  </si>
+  <si>
+    <t>0.9797,0.0107,0.0090,0.0039</t>
+  </si>
+  <si>
+    <t>0.9697,0.0255,0.0123,0.0033</t>
+  </si>
+  <si>
+    <t>0.9743,0.0187,0.0091,0.0039</t>
+  </si>
+  <si>
+    <t>0.9434,0.0669,0.0193,0.0044</t>
+  </si>
+  <si>
+    <t>0.9722,0.0167,0.0191,0.0036</t>
+  </si>
+  <si>
+    <t>0.9867,0.0092,0.0036,0.0021</t>
+  </si>
+  <si>
+    <t>0.9821,0.0100,0.0052,0.0041</t>
+  </si>
+  <si>
+    <t>0.9837,0.0077,0.0064,0.0031</t>
+  </si>
+  <si>
+    <t>0.0232,0.0123,0.9798,0.0019</t>
+  </si>
+  <si>
+    <t>0.1443,0.3914,0.5010,0.0132</t>
+  </si>
+  <si>
+    <t>0.8199,0.0094,0.2704,0.0137</t>
+  </si>
+  <si>
+    <t>0.0305,0.0107,0.9746,0.0035</t>
+  </si>
+  <si>
+    <t>0.0019,0.0073,0.9935,0.0035</t>
+  </si>
+  <si>
+    <t>0.0633,0.0336,0.9393,0.0027</t>
+  </si>
+  <si>
+    <t>0.0069,0.0088,0.9898,0.0032</t>
+  </si>
+  <si>
+    <t>0.0513,0.0119,0.9598,0.0055</t>
+  </si>
+  <si>
+    <t>0.0016,0.0802,0.9939,0.0008</t>
+  </si>
+  <si>
+    <t>0.0229,0.0361,0.9548,0.0100</t>
+  </si>
+  <si>
+    <t>0.1508,0.0439,0.8326,0.0150</t>
+  </si>
+  <si>
+    <t>0.4124,0.0185,0.7006,0.0135</t>
+  </si>
+  <si>
+    <t>0.3639,0.0133,0.7793,0.0065</t>
+  </si>
+  <si>
+    <t>0.5970,0.0123,0.4478,0.0352</t>
+  </si>
+  <si>
+    <t>0.9694,0.0346,0.0066,0.0036</t>
+  </si>
+  <si>
+    <t>0.9788,0.0214,0.0083,0.0018</t>
+  </si>
+  <si>
+    <t>0.9853,0.0120,0.0054,0.0017</t>
+  </si>
+  <si>
+    <t>0.9740,0.0168,0.0175,0.0023</t>
+  </si>
+  <si>
+    <t>0.9852,0.0101,0.0060,0.0026</t>
+  </si>
+  <si>
+    <t>0.9727,0.0280,0.0097,0.0023</t>
+  </si>
+  <si>
+    <t>0.9794,0.0145,0.0102,0.0029</t>
+  </si>
+  <si>
+    <t>0.9854,0.0093,0.0057,0.0027</t>
+  </si>
+  <si>
+    <t>0.0349,0.2020,0.9039,0.0067</t>
+  </si>
+  <si>
+    <t>0.0126,0.0260,0.9755,0.0061</t>
+  </si>
+  <si>
+    <t>0.0198,0.1020,0.9568,0.0036</t>
+  </si>
+  <si>
+    <t>0.0773,0.0340,0.9143,0.0141</t>
+  </si>
+  <si>
+    <t>0.0045,0.0031,0.9890,0.0094</t>
+  </si>
+  <si>
+    <t>0.1643,0.0261,0.8615,0.0232</t>
+  </si>
+  <si>
+    <t>0.0468,0.0356,0.9319,0.0140</t>
+  </si>
+  <si>
+    <t>0.0149,0.0178,0.8712,0.2093</t>
+  </si>
+  <si>
+    <t>0.9500,0.0090,0.0293,0.0169</t>
+  </si>
+  <si>
+    <t>0.0693,0.0911,0.0354,0.9415</t>
+  </si>
+  <si>
+    <t>0.0543,0.0084,0.0183,0.9609</t>
+  </si>
+  <si>
+    <t>0.0481,0.0027,0.0109,0.9671</t>
+  </si>
+  <si>
+    <t>0.0129,0.0120,0.0064,0.9905</t>
+  </si>
+  <si>
+    <t>0.4427,0.0274,0.1068,0.4511</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1987,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2186,7 @@
         <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2365,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2382,7 @@
         <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2449,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2477,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>263</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2911,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2981,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3124,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3586,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3611,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3698,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3709,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3852,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3936,7 @@
         <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4031,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4059,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4087,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,10 +4227,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4353,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4381,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4622,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4636,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4650,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4692,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4717,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4776,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4787,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4818,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4829,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4899,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5182,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5193,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5515,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
